--- a/data/trans_bre/IP16_n_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 21,24</t>
+          <t>-19,42; 22,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 25,54</t>
+          <t>-8,84; 26,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 7,3</t>
+          <t>-23,45; 7,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 36,27</t>
+          <t>-5,98; 35,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 88,99</t>
+          <t>-42,66; 94,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,89; 226,91</t>
+          <t>-37,0; 258,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 186,21</t>
+          <t>-100,0; 259,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 227,93</t>
+          <t>-21,04; 214,53</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 24,9</t>
+          <t>-8,99; 25,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 13,19</t>
+          <t>-12,2; 12,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 14,25</t>
+          <t>-9,07; 14,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 12,86</t>
+          <t>-19,2; 14,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 127,42</t>
+          <t>-24,07; 112,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,18; 263,04</t>
+          <t>-68,56; 246,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,78; 190,44</t>
+          <t>-55,14; 197,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,58; 45,46</t>
+          <t>-48,39; 51,88</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 4,11</t>
+          <t>-36,21; 4,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 22,95</t>
+          <t>-3,93; 21,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 2,56</t>
+          <t>-29,48; 2,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 3,14</t>
+          <t>-37,72; 3,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,54; 11,8</t>
+          <t>-63,03; 16,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,98; 667,96</t>
+          <t>-39,75; 534,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-87,07; 36,21</t>
+          <t>-89,41; 25,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-82,05; 7,58</t>
+          <t>-84,43; 10,88</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 18,27</t>
+          <t>-23,06; 19,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 13,84</t>
+          <t>-12,86; 14,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 18,98</t>
+          <t>-4,6; 19,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 16,73</t>
+          <t>-23,01; 16,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 49,78</t>
+          <t>-43,46; 51,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,94; 148,61</t>
+          <t>-59,8; 184,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 809,77</t>
+          <t>-62,84; 774,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,2; 61,43</t>
+          <t>-50,69; 63,1</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 8,17</t>
+          <t>-10,81; 8,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 11,17</t>
+          <t>-2,75; 11,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 5,62</t>
+          <t>-8,71; 5,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 5,33</t>
+          <t>-18,82; 4,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 22,62</t>
+          <t>-24,67; 23,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 102,95</t>
+          <t>-17,52; 110,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 57,72</t>
+          <t>-50,38; 45,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 17,77</t>
+          <t>-48,87; 14,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16_n_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,78</t>
+          <t>15,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 22,27</t>
+          <t>-18,3; 21,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 26,1</t>
+          <t>-9,79; 27,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 7,33</t>
+          <t>-20,92; 7,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 35,36</t>
+          <t>-8,6; 35,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 94,94</t>
+          <t>-39,85; 82,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 258,16</t>
+          <t>-43,14; 263,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 259,03</t>
+          <t>-100,0; 214,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 214,53</t>
+          <t>-21,82; 199,86</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,09</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-9,06%</t>
+          <t>-1,3%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 25,51</t>
+          <t>-6,43; 25,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 12,35</t>
+          <t>-10,96; 13,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 14,7</t>
+          <t>-9,24; 14,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 14,03</t>
+          <t>-17,08; 16,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 112,01</t>
+          <t>-17,18; 119,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,56; 246,02</t>
+          <t>-65,33; 262,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,14; 197,38</t>
+          <t>-48,98; 222,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 51,88</t>
+          <t>-40,65; 61,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-13,79</t>
+          <t>-2,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-40,45%</t>
+          <t>-7,55%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-36,21; 4,45</t>
+          <t>-32,0; 4,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 21,18</t>
+          <t>-3,66; 22,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 2,17</t>
+          <t>-29,25; 2,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 3,66</t>
+          <t>-18,84; 15,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,03; 16,13</t>
+          <t>-58,13; 12,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,75; 534,96</t>
+          <t>-38,81; 561,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-89,41; 25,18</t>
+          <t>-85,91; 34,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-84,43; 10,88</t>
+          <t>-43,7; 66,6</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,78</t>
+          <t>-3,37</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-7,45%</t>
+          <t>-8,93%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 19,85</t>
+          <t>-21,86; 20,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 14,97</t>
+          <t>-14,15; 12,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 19,02</t>
+          <t>-5,32; 19,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 16,81</t>
+          <t>-24,57; 17,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 51,85</t>
+          <t>-41,38; 55,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,8; 184,71</t>
+          <t>-62,88; 151,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,84; 774,3</t>
+          <t>-68,28; 889,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,69; 63,1</t>
+          <t>-50,94; 68,23</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,08</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-15,13%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 8,21</t>
+          <t>-11,39; 8,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 11,66</t>
+          <t>-3,18; 10,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 5,35</t>
+          <t>-8,63; 5,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 4,52</t>
+          <t>-9,03; 9,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 23,79</t>
+          <t>-26,31; 23,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 110,75</t>
+          <t>-18,56; 101,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 45,66</t>
+          <t>-50,61; 55,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 14,21</t>
+          <t>-23,51; 31,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16_n_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,81</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,04</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-44,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53,85%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.995202964260859</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.886898785783118</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.8101852326304486</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.875172873966963</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2908024137460256</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.4552774614148802</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.3768549034674653</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.7095521591319138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-18,3; 21,57</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,79; 27,79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-20,92; 7,39</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,6; 35,57</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-39,85; 82,5</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-43,14; 263,92</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 214,87</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-21,82; 199,86</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.325885938941052</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.682927841425622</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.431010083850702</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.19067098514524</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3777726210003828</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5371953873482733</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.2339821155310965</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.065792524635177</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.684822893964457</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.380518969825792</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.15989139325934</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.380607841635071</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.741285619413398</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>2.998539530906066</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>8,91</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>24,52%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-1,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,43; 25,2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-10,96; 13,3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,24; 14,33</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-17,08; 16,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-17,18; 119,44</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-65,33; 262,09</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-48,98; 222,87</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-40,65; 61,77</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.463769471430055</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5317937703327298</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9341293552251652</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.586685142793068</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.4199122237447735</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2546474230272326</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.3988741172743475</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1895359445055563</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-15,29</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,09</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-12,58</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-32,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-53,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-7,55%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.508418170845668</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.085894618655719</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.298263474802969</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-6.096656088728068</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2365296338887592</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6132526824848115</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4624520738853673</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5587971863589674</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-32,0; 4,56</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,66; 22,06</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-29,25; 2,43</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-18,84; 15,49</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-58,13; 12,0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-38,81; 561,33</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-85,91; 34,12</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-43,7; 66,6</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.435316248963464</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.896497950949163</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.537697338401222</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.35010605289971</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.530156697905302</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>3.563788315106376</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>3.08272978750352</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3959368092546772</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +815,295 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,68</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,37</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-3,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-8,93%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.255620075465845</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.859191314363041</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.986934580418604</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.2818858848280606</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.4736513880937065</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.9360639227292934</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.5059706584566963</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.02733035317940349</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-21,86; 20,36</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-14,15; 12,98</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 19,62</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-24,57; 17,05</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-41,38; 55,08</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-62,88; 151,69</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-68,28; 889,92</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-50,94; 68,23</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-10.69667394321962</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.781119655110544</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.353659320692167</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.138699157821187</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.734557523483549</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4039991182415829</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.8703989676366463</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4556981637325263</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.2802415084340007</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.994853618019214</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6326094689745645</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.741983619406592</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.02525315579632289</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>6.894473732625354</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3055808967696891</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.7738366191304602</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3.101550398720628</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.4228438853833234</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.133221213432679</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.9117983535903713</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3640118025225371</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1174268690389349</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1.156960146940538</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1296739952995926</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-7.026215232020469</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.432860246263302</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.7578456584713473</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.307817250494306</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6679182761216772</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6936607471034818</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6960700769906961</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5632440393956207</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.3831174472551</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.643068103125551</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.376051435424295</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.591614274110887</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2361990709811393</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.38383301281738</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="n">
+        <v>0.8245140119990002</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,85%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-9,02%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-11,39; 8,41</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,18; 10,68</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-8,63; 5,45</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-9,03; 9,45</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-26,31; 23,04</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-18,56; 101,71</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-50,61; 55,0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-23,51; 31,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.8845601850296481</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8161231071238287</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.01208570152467746</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.08806494941568654</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1116373913155507</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.280956543191493</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.005295870280581951</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.01102041115561363</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.082796076147634</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.6879490424069717</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.22317471121803</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.565536708011636</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3495106760527131</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2045587313896238</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4327395411556695</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2820297128167414</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.441513528997812</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.544337762016866</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.18784936892884</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.319354524663664</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.212741403429535</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.205557806914321</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.7238265048067668</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3328319999024059</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1111,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
